--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.02549810320551</v>
+        <v>6.829143441770895</v>
       </c>
       <c r="D2" t="n">
-        <v>15.49618600958149</v>
+        <v>2.518130226556992</v>
       </c>
       <c r="E2" t="n">
-        <v>13.84007577005292</v>
+        <v>2.249012312633599</v>
       </c>
       <c r="F2" t="n">
-        <v>11.6404172429513</v>
+        <v>1.891567801979585</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.58938921627471</v>
+        <v>5.133275747644642</v>
       </c>
       <c r="D3" t="n">
-        <v>20.97762085085452</v>
+        <v>3.40886338826386</v>
       </c>
       <c r="E3" t="n">
-        <v>13.84007577005292</v>
+        <v>2.249012312633599</v>
       </c>
       <c r="F3" t="n">
-        <v>11.6404172429513</v>
+        <v>1.891567801979585</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.31781466990875</v>
+        <v>5.739144883860172</v>
       </c>
       <c r="D4" t="n">
-        <v>12.02586743320736</v>
+        <v>1.954203457896197</v>
       </c>
       <c r="E4" t="n">
-        <v>13.84007577005292</v>
+        <v>2.249012312633599</v>
       </c>
       <c r="F4" t="n">
-        <v>11.6404172429513</v>
+        <v>1.891567801979585</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.7843022971846</v>
+        <v>3.052449123292498</v>
       </c>
       <c r="D5" t="n">
-        <v>16.58627910682721</v>
+        <v>2.695270354859421</v>
       </c>
       <c r="E5" t="n">
-        <v>13.84007577005292</v>
+        <v>2.249012312633599</v>
       </c>
       <c r="F5" t="n">
-        <v>11.6404172429513</v>
+        <v>1.891567801979585</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.77425213367133</v>
+        <v>5.000815971721591</v>
       </c>
       <c r="D6" t="n">
-        <v>38.79343117135684</v>
+        <v>6.303932565345487</v>
       </c>
       <c r="E6" t="n">
-        <v>13.84007577005292</v>
+        <v>2.249012312633599</v>
       </c>
       <c r="F6" t="n">
-        <v>11.6404172429513</v>
+        <v>1.891567801979585</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.19975400598958</v>
+        <v>2.957460025973307</v>
       </c>
       <c r="D7" t="n">
-        <v>13.7429717270134</v>
+        <v>2.233232905639677</v>
       </c>
       <c r="E7" t="n">
-        <v>13.84007577005292</v>
+        <v>2.249012312633599</v>
       </c>
       <c r="F7" t="n">
-        <v>11.6404172429513</v>
+        <v>1.891567801979585</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.002808463529457</v>
+        <v>1.300456375323537</v>
       </c>
       <c r="D8" t="n">
-        <v>9.819253572342424</v>
+        <v>1.595628705505644</v>
       </c>
       <c r="E8" t="n">
-        <v>13.84007577005292</v>
+        <v>2.249012312633599</v>
       </c>
       <c r="F8" t="n">
-        <v>11.6404172429513</v>
+        <v>1.891567801979585</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>39.25179998788323</v>
+        <v>6.378417498031025</v>
       </c>
       <c r="D9" t="n">
-        <v>33.11777304039095</v>
+        <v>5.381638119063529</v>
       </c>
       <c r="E9" t="n">
-        <v>13.84007577005292</v>
+        <v>2.249012312633599</v>
       </c>
       <c r="F9" t="n">
-        <v>11.6404172429513</v>
+        <v>1.891567801979585</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.67691437189617</v>
+        <v>4.009998585433128</v>
       </c>
       <c r="D10" t="n">
-        <v>18.27642683288442</v>
+        <v>2.969919360343719</v>
       </c>
       <c r="E10" t="n">
-        <v>13.84007577005292</v>
+        <v>2.249012312633599</v>
       </c>
       <c r="F10" t="n">
-        <v>11.6404172429513</v>
+        <v>1.891567801979585</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>52.93126444247429</v>
+        <v>8.601330471902072</v>
       </c>
       <c r="D11" t="n">
-        <v>42.88035350312877</v>
+        <v>6.968057444258426</v>
       </c>
       <c r="E11" t="n">
-        <v>13.84007577005292</v>
+        <v>2.249012312633599</v>
       </c>
       <c r="F11" t="n">
-        <v>11.6404172429513</v>
+        <v>1.891567801979585</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>5.725546866151939</v>
+        <v>0.9304013657496901</v>
       </c>
       <c r="D12" t="n">
-        <v>5.70087712549569</v>
+        <v>0.9263925328930496</v>
       </c>
       <c r="E12" t="n">
-        <v>13.84007577005292</v>
+        <v>2.249012312633599</v>
       </c>
       <c r="F12" t="n">
-        <v>11.6404172429513</v>
+        <v>1.891567801979585</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
